--- a/old_conf.xlsx
+++ b/old_conf.xlsx
@@ -618,112 +618,112 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>-174</v>
+        <v>-39</v>
       </c>
       <c r="B2">
-        <v>-75</v>
+        <v>-186</v>
       </c>
       <c r="C2">
-        <v>-23</v>
+        <v>-115</v>
       </c>
       <c r="D2">
-        <v>-222</v>
+        <v>-111</v>
       </c>
       <c r="E2">
-        <v>-24</v>
+        <v>-258</v>
       </c>
       <c r="F2">
-        <v>-127</v>
+        <v>-343</v>
       </c>
       <c r="G2">
-        <v>178</v>
+        <v>110</v>
       </c>
       <c r="H2">
-        <v>27</v>
+        <v>338</v>
       </c>
       <c r="I2">
-        <v>74</v>
+        <v>187</v>
       </c>
       <c r="J2">
-        <v>122</v>
+        <v>183</v>
       </c>
       <c r="K2">
-        <v>173</v>
+        <v>118</v>
       </c>
       <c r="L2">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="M2">
-        <v>-26</v>
+        <v>-333</v>
       </c>
       <c r="N2">
-        <v>-130</v>
+        <v>-256</v>
       </c>
       <c r="O2">
-        <v>-77</v>
+        <v>-193</v>
       </c>
       <c r="P2">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="Q2">
-        <v>175</v>
+        <v>264</v>
       </c>
       <c r="R2">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="S2">
-        <v>-79</v>
+        <v>-110</v>
       </c>
       <c r="T2">
-        <v>-175</v>
+        <v>-183</v>
       </c>
       <c r="U2">
-        <v>-129</v>
+        <v>-340</v>
       </c>
       <c r="V2">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="W2">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="X2">
-        <v>127</v>
+        <v>195</v>
       </c>
       <c r="Y2">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="Z2">
         <v>270</v>
       </c>
       <c r="AA2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AB2">
         <v>0</v>
       </c>
       <c r="AC2">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AD2">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AG2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AH2">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AI2">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AJ2">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -752,45 +752,45 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>L0.png</t>
         </is>
       </c>
       <c r="AW2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -806,94 +806,94 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>-76</v>
+        <v>-334</v>
       </c>
       <c r="B3">
-        <v>-123</v>
+        <v>-118</v>
       </c>
       <c r="C3">
-        <v>-25</v>
+        <v>-193</v>
       </c>
       <c r="D3">
-        <v>-76</v>
+        <v>-334</v>
       </c>
       <c r="E3">
-        <v>-127</v>
+        <v>-257</v>
       </c>
       <c r="F3">
-        <v>-175</v>
+        <v>-184</v>
       </c>
       <c r="G3">
-        <v>226</v>
+        <v>336</v>
       </c>
       <c r="H3">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="I3">
-        <v>126</v>
+        <v>259</v>
       </c>
       <c r="J3">
-        <v>229</v>
+        <v>266</v>
       </c>
       <c r="K3">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="L3">
-        <v>120</v>
+        <v>189</v>
       </c>
       <c r="M3">
-        <v>-171</v>
+        <v>-108</v>
       </c>
       <c r="N3">
-        <v>-228</v>
+        <v>-192</v>
       </c>
       <c r="O3">
-        <v>-26</v>
+        <v>-270</v>
       </c>
       <c r="P3">
-        <v>220</v>
+        <v>193</v>
       </c>
       <c r="Q3">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="R3">
-        <v>173</v>
+        <v>334</v>
       </c>
       <c r="S3">
-        <v>-229</v>
+        <v>-34</v>
       </c>
       <c r="T3">
-        <v>-71</v>
+        <v>-334</v>
       </c>
       <c r="U3">
-        <v>-177</v>
+        <v>-106</v>
       </c>
       <c r="V3">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="W3">
-        <v>125</v>
+        <v>334</v>
       </c>
       <c r="X3">
-        <v>171</v>
+        <v>39</v>
       </c>
       <c r="Y3">
         <v>270</v>
       </c>
       <c r="Z3">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AA3">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AE3">
         <v>270</v>
@@ -902,20 +902,20 @@
         <v>90</v>
       </c>
       <c r="AG3">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AH3">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AI3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="AW3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
@@ -994,112 +994,112 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>-171</v>
+        <v>-269</v>
       </c>
       <c r="B4">
-        <v>-228</v>
+        <v>-38</v>
       </c>
       <c r="C4">
-        <v>-127</v>
+        <v>-115</v>
       </c>
       <c r="D4">
-        <v>-78</v>
+        <v>-268</v>
       </c>
       <c r="E4">
-        <v>-175</v>
+        <v>-31</v>
       </c>
       <c r="F4">
-        <v>-20</v>
+        <v>-116</v>
       </c>
       <c r="G4">
-        <v>127</v>
+        <v>180</v>
       </c>
       <c r="H4">
-        <v>76</v>
+        <v>33</v>
       </c>
       <c r="I4">
-        <v>176</v>
+        <v>263</v>
       </c>
       <c r="J4">
-        <v>127</v>
+        <v>270</v>
       </c>
       <c r="K4">
-        <v>71</v>
+        <v>105</v>
       </c>
       <c r="L4">
-        <v>224</v>
+        <v>336</v>
       </c>
       <c r="M4">
-        <v>-73</v>
+        <v>-186</v>
       </c>
       <c r="N4">
-        <v>-21</v>
+        <v>-34</v>
       </c>
       <c r="O4">
-        <v>-127</v>
+        <v>-344</v>
       </c>
       <c r="P4">
-        <v>129</v>
+        <v>182</v>
       </c>
       <c r="Q4">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="R4">
-        <v>22</v>
+        <v>119</v>
       </c>
       <c r="S4">
-        <v>-172</v>
+        <v>-339</v>
       </c>
       <c r="T4">
-        <v>-120</v>
+        <v>-36</v>
       </c>
       <c r="U4">
-        <v>-26</v>
+        <v>-256</v>
       </c>
       <c r="V4">
-        <v>174</v>
+        <v>113</v>
       </c>
       <c r="W4">
-        <v>27</v>
+        <v>188</v>
       </c>
       <c r="X4">
-        <v>122</v>
+        <v>331</v>
       </c>
       <c r="Y4">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AA4">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AB4">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AC4">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>180</v>
       </c>
       <c r="AF4">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AG4">
         <v>270</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AI4">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
@@ -1143,14 +1143,14 @@
       </c>
       <c r="AS4" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AU4" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -1162,11 +1162,11 @@
         </is>
       </c>
       <c r="AW4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1182,133 +1182,133 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>-20</v>
+        <v>-111</v>
       </c>
       <c r="B5">
-        <v>-177</v>
+        <v>-269</v>
       </c>
       <c r="C5">
-        <v>-73</v>
+        <v>-331</v>
       </c>
       <c r="D5">
-        <v>-178</v>
+        <v>-40</v>
       </c>
       <c r="E5">
-        <v>-124</v>
+        <v>-118</v>
       </c>
       <c r="F5">
-        <v>-228</v>
+        <v>-263</v>
       </c>
       <c r="G5">
-        <v>125</v>
+        <v>188</v>
       </c>
       <c r="H5">
-        <v>73</v>
+        <v>345</v>
       </c>
       <c r="I5">
-        <v>229</v>
+        <v>268</v>
       </c>
       <c r="J5">
-        <v>28</v>
+        <v>341</v>
       </c>
       <c r="K5">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="L5">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="M5">
-        <v>-173</v>
+        <v>-111</v>
       </c>
       <c r="N5">
-        <v>-226</v>
+        <v>-264</v>
       </c>
       <c r="O5">
-        <v>-129</v>
+        <v>-31</v>
       </c>
       <c r="P5">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="Q5">
-        <v>129</v>
+        <v>255</v>
       </c>
       <c r="R5">
-        <v>222</v>
+        <v>336</v>
       </c>
       <c r="S5">
-        <v>-171</v>
+        <v>-195</v>
       </c>
       <c r="T5">
-        <v>-29</v>
+        <v>-335</v>
       </c>
       <c r="U5">
-        <v>-129</v>
+        <v>-37</v>
       </c>
       <c r="V5">
-        <v>75</v>
+        <v>264</v>
       </c>
       <c r="W5">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="X5">
-        <v>223</v>
+        <v>182</v>
       </c>
       <c r="Y5">
         <v>90</v>
       </c>
       <c r="Z5">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AA5">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AB5">
         <v>270</v>
       </c>
       <c r="AC5">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AD5">
         <v>180</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AF5">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AG5">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AI5">
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -1350,11 +1350,11 @@
         </is>
       </c>
       <c r="AW5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1370,112 +1370,112 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>-225</v>
+        <v>-267</v>
       </c>
       <c r="B6">
-        <v>-179</v>
+        <v>-108</v>
       </c>
       <c r="C6">
-        <v>-77</v>
+        <v>-32</v>
       </c>
       <c r="D6">
-        <v>-220</v>
+        <v>-40</v>
       </c>
       <c r="E6">
-        <v>-124</v>
+        <v>-181</v>
       </c>
       <c r="F6">
-        <v>-21</v>
+        <v>-113</v>
       </c>
       <c r="G6">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="H6">
-        <v>173</v>
+        <v>262</v>
       </c>
       <c r="I6">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="J6">
-        <v>78</v>
+        <v>189</v>
       </c>
       <c r="K6">
-        <v>26</v>
+        <v>339</v>
       </c>
       <c r="L6">
-        <v>224</v>
+        <v>267</v>
       </c>
       <c r="M6">
-        <v>-178</v>
+        <v>-260</v>
       </c>
       <c r="N6">
-        <v>-79</v>
+        <v>-184</v>
       </c>
       <c r="O6">
-        <v>-230</v>
+        <v>-108</v>
       </c>
       <c r="P6">
-        <v>174</v>
+        <v>265</v>
       </c>
       <c r="Q6">
-        <v>28</v>
+        <v>338</v>
       </c>
       <c r="R6">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="S6">
-        <v>-121</v>
+        <v>-32</v>
       </c>
       <c r="T6">
-        <v>-228</v>
+        <v>-116</v>
       </c>
       <c r="U6">
-        <v>-170</v>
+        <v>-194</v>
       </c>
       <c r="V6">
-        <v>127</v>
+        <v>187</v>
       </c>
       <c r="W6">
-        <v>176</v>
+        <v>109</v>
       </c>
       <c r="X6">
-        <v>22</v>
+        <v>331</v>
       </c>
       <c r="Y6">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="Z6">
         <v>180</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AC6">
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AE6">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AF6">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AG6">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AH6">
         <v>90</v>
       </c>
       <c r="AI6">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1558,116 +1558,116 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>-75</v>
+        <v>-36</v>
       </c>
       <c r="B7">
-        <v>-121</v>
+        <v>-268</v>
       </c>
       <c r="C7">
-        <v>-222</v>
+        <v>-183</v>
       </c>
       <c r="D7">
-        <v>-230</v>
+        <v>-42</v>
       </c>
       <c r="E7">
-        <v>-71</v>
+        <v>-264</v>
       </c>
       <c r="F7">
-        <v>-23</v>
+        <v>-180</v>
       </c>
       <c r="G7">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="H7">
-        <v>225</v>
+        <v>43</v>
       </c>
       <c r="I7">
-        <v>176</v>
+        <v>337</v>
       </c>
       <c r="J7">
-        <v>74</v>
+        <v>334</v>
       </c>
       <c r="K7">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="L7">
-        <v>223</v>
+        <v>106</v>
       </c>
       <c r="M7">
-        <v>-120</v>
+        <v>-33</v>
       </c>
       <c r="N7">
-        <v>-77</v>
+        <v>-110</v>
       </c>
       <c r="O7">
-        <v>-223</v>
+        <v>-257</v>
       </c>
       <c r="P7">
-        <v>120</v>
+        <v>336</v>
       </c>
       <c r="Q7">
-        <v>28</v>
+        <v>268</v>
       </c>
       <c r="R7">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="S7">
-        <v>-179</v>
+        <v>-261</v>
       </c>
       <c r="T7">
-        <v>-72</v>
+        <v>-115</v>
       </c>
       <c r="U7">
-        <v>-28</v>
+        <v>-187</v>
       </c>
       <c r="V7">
-        <v>77</v>
+        <v>257</v>
       </c>
       <c r="W7">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="X7">
-        <v>224</v>
+        <v>44</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AA7">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AB7">
         <v>180</v>
       </c>
       <c r="AC7">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AD7">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AF7">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AG7">
         <v>270</v>
       </c>
       <c r="AH7">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AI7">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -1722,11 +1722,11 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AW7">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1746,112 +1746,112 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>-229</v>
+        <v>-185</v>
       </c>
       <c r="B8">
-        <v>-79</v>
+        <v>-43</v>
       </c>
       <c r="C8">
-        <v>-175</v>
+        <v>-334</v>
       </c>
       <c r="D8">
-        <v>-80</v>
+        <v>-39</v>
       </c>
       <c r="E8">
-        <v>-124</v>
+        <v>-266</v>
       </c>
       <c r="F8">
-        <v>-25</v>
+        <v>-181</v>
       </c>
       <c r="G8">
-        <v>78</v>
+        <v>181</v>
       </c>
       <c r="H8">
-        <v>28</v>
+        <v>118</v>
       </c>
       <c r="I8">
-        <v>223</v>
+        <v>262</v>
       </c>
       <c r="J8">
-        <v>223</v>
+        <v>340</v>
       </c>
       <c r="K8">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="L8">
-        <v>121</v>
+        <v>260</v>
       </c>
       <c r="M8">
-        <v>-221</v>
+        <v>-185</v>
       </c>
       <c r="N8">
-        <v>-21</v>
+        <v>-41</v>
       </c>
       <c r="O8">
-        <v>-78</v>
+        <v>-115</v>
       </c>
       <c r="P8">
-        <v>223</v>
+        <v>31</v>
       </c>
       <c r="Q8">
-        <v>178</v>
+        <v>334</v>
       </c>
       <c r="R8">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="S8">
-        <v>-79</v>
+        <v>-117</v>
       </c>
       <c r="T8">
-        <v>-173</v>
+        <v>-43</v>
       </c>
       <c r="U8">
-        <v>-21</v>
+        <v>-334</v>
       </c>
       <c r="V8">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="W8">
-        <v>126</v>
+        <v>255</v>
       </c>
       <c r="X8">
-        <v>227</v>
+        <v>106</v>
       </c>
       <c r="Y8">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="Z8">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AA8">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AC8">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AE8">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AF8">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AG8">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AJ8">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
@@ -1870,14 +1870,14 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AP8" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -1914,11 +1914,11 @@
         </is>
       </c>
       <c r="AW8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1934,112 +1934,112 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>-179</v>
+        <v>-118</v>
       </c>
       <c r="B9">
-        <v>-28</v>
+        <v>-265</v>
       </c>
       <c r="C9">
-        <v>-123</v>
+        <v>-334</v>
       </c>
       <c r="D9">
-        <v>-224</v>
+        <v>-262</v>
       </c>
       <c r="E9">
-        <v>-27</v>
+        <v>-340</v>
       </c>
       <c r="F9">
+        <v>-184</v>
+      </c>
+      <c r="G9">
+        <v>36</v>
+      </c>
+      <c r="H9">
+        <v>181</v>
+      </c>
+      <c r="I9">
+        <v>261</v>
+      </c>
+      <c r="J9">
+        <v>263</v>
+      </c>
+      <c r="K9">
+        <v>41</v>
+      </c>
+      <c r="L9">
+        <v>184</v>
+      </c>
+      <c r="M9">
+        <v>-42</v>
+      </c>
+      <c r="N9">
+        <v>-258</v>
+      </c>
+      <c r="O9">
+        <v>-184</v>
+      </c>
+      <c r="P9">
+        <v>34</v>
+      </c>
+      <c r="Q9">
+        <v>110</v>
+      </c>
+      <c r="R9">
+        <v>267</v>
+      </c>
+      <c r="S9">
         <v>-180</v>
       </c>
-      <c r="G9">
-        <v>228</v>
-      </c>
-      <c r="H9">
-        <v>125</v>
-      </c>
-      <c r="I9">
-        <v>71</v>
-      </c>
-      <c r="J9">
-        <v>72</v>
-      </c>
-      <c r="K9">
-        <v>172</v>
-      </c>
-      <c r="L9">
-        <v>227</v>
-      </c>
-      <c r="M9">
-        <v>-77</v>
-      </c>
-      <c r="N9">
-        <v>-29</v>
-      </c>
-      <c r="O9">
-        <v>-126</v>
-      </c>
-      <c r="P9">
-        <v>124</v>
-      </c>
-      <c r="Q9">
-        <v>77</v>
-      </c>
-      <c r="R9">
-        <v>24</v>
-      </c>
-      <c r="S9">
-        <v>-28</v>
-      </c>
       <c r="T9">
-        <v>-173</v>
+        <v>-116</v>
       </c>
       <c r="U9">
-        <v>-130</v>
+        <v>-332</v>
       </c>
       <c r="V9">
-        <v>222</v>
+        <v>117</v>
       </c>
       <c r="W9">
-        <v>25</v>
+        <v>262</v>
       </c>
       <c r="X9">
-        <v>127</v>
+        <v>331</v>
       </c>
       <c r="Y9">
         <v>180</v>
       </c>
       <c r="Z9">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AA9">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AB9">
         <v>270</v>
       </c>
       <c r="AC9">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AD9">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AG9">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AI9">
         <v>90</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -2102,11 +2102,11 @@
         </is>
       </c>
       <c r="AW9">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -2122,103 +2122,103 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>-128</v>
+        <v>-106</v>
       </c>
       <c r="B10">
-        <v>-74</v>
+        <v>-344</v>
       </c>
       <c r="C10">
-        <v>-177</v>
+        <v>-189</v>
       </c>
       <c r="D10">
-        <v>-178</v>
+        <v>-109</v>
       </c>
       <c r="E10">
-        <v>-25</v>
+        <v>-330</v>
       </c>
       <c r="F10">
-        <v>-226</v>
+        <v>-257</v>
       </c>
       <c r="G10">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="H10">
-        <v>177</v>
+        <v>117</v>
       </c>
       <c r="I10">
-        <v>228</v>
+        <v>257</v>
       </c>
       <c r="J10">
-        <v>221</v>
+        <v>268</v>
       </c>
       <c r="K10">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="L10">
-        <v>30</v>
+        <v>183</v>
       </c>
       <c r="M10">
-        <v>-173</v>
+        <v>-30</v>
       </c>
       <c r="N10">
-        <v>-78</v>
+        <v>-186</v>
       </c>
       <c r="O10">
-        <v>-225</v>
+        <v>-266</v>
       </c>
       <c r="P10">
-        <v>121</v>
+        <v>259</v>
       </c>
       <c r="Q10">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="R10">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="S10">
-        <v>-30</v>
+        <v>-194</v>
       </c>
       <c r="T10">
-        <v>-223</v>
+        <v>-44</v>
       </c>
       <c r="U10">
-        <v>-129</v>
+        <v>-117</v>
       </c>
       <c r="V10">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="W10">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="X10">
-        <v>178</v>
+        <v>256</v>
       </c>
       <c r="Y10">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="Z10">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AA10">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AC10">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AD10">
         <v>90</v>
       </c>
       <c r="AE10">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AF10">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AH10">
         <v>0</v>
@@ -2266,35 +2266,35 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>L0.png</t>
         </is>
       </c>
       <c r="AW10">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -2310,109 +2310,109 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>-177</v>
+        <v>-191</v>
       </c>
       <c r="B11">
-        <v>-126</v>
+        <v>-108</v>
       </c>
       <c r="C11">
-        <v>-71</v>
+        <v>-344</v>
       </c>
       <c r="D11">
-        <v>-78</v>
+        <v>-265</v>
       </c>
       <c r="E11">
-        <v>-229</v>
+        <v>-118</v>
       </c>
       <c r="F11">
-        <v>-173</v>
+        <v>-44</v>
       </c>
       <c r="G11">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="H11">
-        <v>173</v>
+        <v>39</v>
       </c>
       <c r="I11">
-        <v>228</v>
+        <v>340</v>
       </c>
       <c r="J11">
-        <v>72</v>
+        <v>267</v>
       </c>
       <c r="K11">
-        <v>177</v>
+        <v>343</v>
       </c>
       <c r="L11">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="M11">
-        <v>-22</v>
+        <v>-344</v>
       </c>
       <c r="N11">
-        <v>-225</v>
+        <v>-37</v>
       </c>
       <c r="O11">
-        <v>-123</v>
+        <v>-269</v>
       </c>
       <c r="P11">
-        <v>28</v>
+        <v>262</v>
       </c>
       <c r="Q11">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="R11">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="S11">
-        <v>-224</v>
+        <v>-112</v>
       </c>
       <c r="T11">
-        <v>-178</v>
+        <v>-267</v>
       </c>
       <c r="U11">
-        <v>-27</v>
+        <v>-187</v>
       </c>
       <c r="V11">
-        <v>80</v>
+        <v>266</v>
       </c>
       <c r="W11">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="X11">
-        <v>225</v>
+        <v>39</v>
       </c>
       <c r="Y11">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AA11">
         <v>180</v>
       </c>
       <c r="AB11">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AF11">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AG11">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ11">
         <v>270</v>
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2498,97 +2498,97 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>-220</v>
+        <v>-267</v>
       </c>
       <c r="B12">
-        <v>-23</v>
+        <v>-115</v>
       </c>
       <c r="C12">
-        <v>-171</v>
+        <v>-339</v>
       </c>
       <c r="D12">
-        <v>-174</v>
+        <v>-333</v>
       </c>
       <c r="E12">
-        <v>-22</v>
+        <v>-189</v>
       </c>
       <c r="F12">
-        <v>-229</v>
+        <v>-108</v>
       </c>
       <c r="G12">
-        <v>26</v>
+        <v>257</v>
       </c>
       <c r="H12">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="I12">
-        <v>73</v>
+        <v>192</v>
       </c>
       <c r="J12">
-        <v>229</v>
+        <v>342</v>
       </c>
       <c r="K12">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="L12">
-        <v>21</v>
+        <v>256</v>
       </c>
       <c r="M12">
-        <v>-173</v>
+        <v>-266</v>
       </c>
       <c r="N12">
-        <v>-70</v>
+        <v>-343</v>
       </c>
       <c r="O12">
-        <v>-123</v>
+        <v>-110</v>
       </c>
       <c r="P12">
-        <v>224</v>
+        <v>259</v>
       </c>
       <c r="Q12">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="R12">
-        <v>122</v>
+        <v>183</v>
       </c>
       <c r="S12">
-        <v>-180</v>
+        <v>-39</v>
       </c>
       <c r="T12">
-        <v>-130</v>
+        <v>-262</v>
       </c>
       <c r="U12">
-        <v>-79</v>
+        <v>-119</v>
       </c>
       <c r="V12">
-        <v>75</v>
+        <v>333</v>
       </c>
       <c r="W12">
-        <v>222</v>
+        <v>266</v>
       </c>
       <c r="X12">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="Y12">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="Z12">
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB12">
         <v>270</v>
       </c>
       <c r="AC12">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AD12">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AE12">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AF12">
         <v>90</v>
@@ -2597,13 +2597,13 @@
         <v>0</v>
       </c>
       <c r="AH12">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AI12">
         <v>180</v>
       </c>
       <c r="AJ12">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -2662,11 +2662,11 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AW12">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
@@ -2686,112 +2686,112 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>-223</v>
+        <v>-31</v>
       </c>
       <c r="B13">
-        <v>-78</v>
+        <v>-342</v>
       </c>
       <c r="C13">
-        <v>-123</v>
+        <v>-117</v>
       </c>
       <c r="D13">
-        <v>-74</v>
+        <v>-260</v>
       </c>
       <c r="E13">
-        <v>-230</v>
+        <v>-187</v>
       </c>
       <c r="F13">
-        <v>-126</v>
+        <v>-36</v>
       </c>
       <c r="G13">
-        <v>224</v>
+        <v>30</v>
       </c>
       <c r="H13">
-        <v>128</v>
+        <v>263</v>
       </c>
       <c r="I13">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="J13">
-        <v>25</v>
+        <v>259</v>
       </c>
       <c r="K13">
-        <v>222</v>
+        <v>120</v>
       </c>
       <c r="L13">
-        <v>171</v>
+        <v>41</v>
       </c>
       <c r="M13">
-        <v>-178</v>
+        <v>-110</v>
       </c>
       <c r="N13">
-        <v>-225</v>
+        <v>-32</v>
       </c>
       <c r="O13">
-        <v>-22</v>
+        <v>-256</v>
       </c>
       <c r="P13">
-        <v>128</v>
+        <v>44</v>
       </c>
       <c r="Q13">
-        <v>172</v>
+        <v>110</v>
       </c>
       <c r="R13">
-        <v>22</v>
+        <v>261</v>
       </c>
       <c r="S13">
-        <v>-25</v>
+        <v>-343</v>
       </c>
       <c r="T13">
-        <v>-70</v>
+        <v>-116</v>
       </c>
       <c r="U13">
-        <v>-226</v>
+        <v>-258</v>
       </c>
       <c r="V13">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="W13">
-        <v>24</v>
+        <v>341</v>
       </c>
       <c r="X13">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="Y13">
         <v>90</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AA13">
         <v>270</v>
       </c>
       <c r="AB13">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AC13">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AD13">
         <v>90</v>
       </c>
       <c r="AE13">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AG13">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AI13">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AJ13">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
@@ -2845,20 +2845,20 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AW13">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">

--- a/old_conf.xlsx
+++ b/old_conf.xlsx
@@ -618,112 +618,112 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>-39</v>
+        <v>-288</v>
       </c>
       <c r="B2">
-        <v>-186</v>
+        <v>-212</v>
       </c>
       <c r="C2">
-        <v>-115</v>
+        <v>-379</v>
       </c>
       <c r="D2">
-        <v>-111</v>
+        <v>-48</v>
       </c>
       <c r="E2">
-        <v>-258</v>
+        <v>-127</v>
       </c>
       <c r="F2">
-        <v>-343</v>
+        <v>-378</v>
       </c>
       <c r="G2">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="H2">
-        <v>338</v>
+        <v>211</v>
       </c>
       <c r="I2">
-        <v>187</v>
+        <v>126</v>
       </c>
       <c r="J2">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="K2">
-        <v>118</v>
+        <v>295</v>
       </c>
       <c r="L2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M2">
-        <v>-333</v>
+        <v>-38</v>
       </c>
       <c r="N2">
-        <v>-256</v>
+        <v>-368</v>
       </c>
       <c r="O2">
-        <v>-193</v>
+        <v>-127</v>
       </c>
       <c r="P2">
-        <v>109</v>
+        <v>288</v>
       </c>
       <c r="Q2">
-        <v>264</v>
+        <v>202</v>
       </c>
       <c r="R2">
-        <v>39</v>
+        <v>129</v>
       </c>
       <c r="S2">
-        <v>-110</v>
+        <v>-129</v>
       </c>
       <c r="T2">
-        <v>-183</v>
+        <v>-369</v>
       </c>
       <c r="U2">
-        <v>-340</v>
+        <v>-40</v>
       </c>
       <c r="V2">
-        <v>258</v>
+        <v>372</v>
       </c>
       <c r="W2">
-        <v>37</v>
+        <v>121</v>
       </c>
       <c r="X2">
-        <v>195</v>
+        <v>290</v>
       </c>
       <c r="Y2">
         <v>0</v>
       </c>
       <c r="Z2">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AA2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AC2">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AD2">
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AF2">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AG2">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AH2">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AI2">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AJ2">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="AW2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
@@ -806,94 +806,94 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>-334</v>
+        <v>-295</v>
       </c>
       <c r="B3">
+        <v>-121</v>
+      </c>
+      <c r="C3">
+        <v>-36</v>
+      </c>
+      <c r="D3">
+        <v>-34</v>
+      </c>
+      <c r="E3">
+        <v>-214</v>
+      </c>
+      <c r="F3">
+        <v>-290</v>
+      </c>
+      <c r="G3">
+        <v>381</v>
+      </c>
+      <c r="H3">
+        <v>208</v>
+      </c>
+      <c r="I3">
+        <v>119</v>
+      </c>
+      <c r="J3">
+        <v>381</v>
+      </c>
+      <c r="K3">
+        <v>40</v>
+      </c>
+      <c r="L3">
+        <v>295</v>
+      </c>
+      <c r="M3">
+        <v>-38</v>
+      </c>
+      <c r="N3">
+        <v>-284</v>
+      </c>
+      <c r="O3">
         <v>-118</v>
       </c>
-      <c r="C3">
-        <v>-193</v>
-      </c>
-      <c r="D3">
-        <v>-334</v>
-      </c>
-      <c r="E3">
-        <v>-257</v>
-      </c>
-      <c r="F3">
-        <v>-184</v>
-      </c>
-      <c r="G3">
-        <v>336</v>
-      </c>
-      <c r="H3">
-        <v>182</v>
-      </c>
-      <c r="I3">
-        <v>259</v>
-      </c>
-      <c r="J3">
-        <v>266</v>
-      </c>
-      <c r="K3">
-        <v>113</v>
-      </c>
-      <c r="L3">
-        <v>189</v>
-      </c>
-      <c r="M3">
-        <v>-108</v>
-      </c>
-      <c r="N3">
-        <v>-192</v>
-      </c>
-      <c r="O3">
-        <v>-270</v>
-      </c>
       <c r="P3">
-        <v>193</v>
+        <v>295</v>
       </c>
       <c r="Q3">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="R3">
-        <v>334</v>
+        <v>213</v>
       </c>
       <c r="S3">
-        <v>-34</v>
+        <v>-36</v>
       </c>
       <c r="T3">
-        <v>-334</v>
+        <v>-372</v>
       </c>
       <c r="U3">
-        <v>-106</v>
+        <v>-209</v>
       </c>
       <c r="V3">
-        <v>185</v>
+        <v>376</v>
       </c>
       <c r="W3">
-        <v>334</v>
+        <v>203</v>
       </c>
       <c r="X3">
-        <v>39</v>
+        <v>291</v>
       </c>
       <c r="Y3">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="Z3">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AB3">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AC3">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AD3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>270</v>
@@ -902,62 +902,62 @@
         <v>90</v>
       </c>
       <c r="AG3">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AH3">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -974,11 +974,11 @@
         </is>
       </c>
       <c r="AW3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -994,76 +994,76 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>-269</v>
+        <v>-116</v>
       </c>
       <c r="B4">
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="C4">
-        <v>-115</v>
+        <v>-206</v>
       </c>
       <c r="D4">
-        <v>-268</v>
+        <v>-125</v>
       </c>
       <c r="E4">
-        <v>-31</v>
+        <v>-294</v>
       </c>
       <c r="F4">
-        <v>-116</v>
+        <v>-46</v>
       </c>
       <c r="G4">
-        <v>180</v>
+        <v>285</v>
       </c>
       <c r="H4">
-        <v>33</v>
+        <v>204</v>
       </c>
       <c r="I4">
-        <v>263</v>
+        <v>376</v>
       </c>
       <c r="J4">
-        <v>270</v>
+        <v>378</v>
       </c>
       <c r="K4">
-        <v>105</v>
+        <v>43</v>
       </c>
       <c r="L4">
-        <v>336</v>
+        <v>289</v>
       </c>
       <c r="M4">
-        <v>-186</v>
+        <v>-294</v>
       </c>
       <c r="N4">
         <v>-34</v>
       </c>
       <c r="O4">
-        <v>-344</v>
+        <v>-368</v>
       </c>
       <c r="P4">
-        <v>182</v>
+        <v>33</v>
       </c>
       <c r="Q4">
-        <v>32</v>
+        <v>209</v>
       </c>
       <c r="R4">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="S4">
-        <v>-339</v>
+        <v>-41</v>
       </c>
       <c r="T4">
-        <v>-36</v>
+        <v>-213</v>
       </c>
       <c r="U4">
-        <v>-256</v>
+        <v>-286</v>
       </c>
       <c r="V4">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="W4">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="X4">
-        <v>331</v>
+        <v>292</v>
       </c>
       <c r="Y4">
         <v>90</v>
@@ -1072,34 +1072,34 @@
         <v>90</v>
       </c>
       <c r="AA4">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AE4">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AG4">
         <v>270</v>
       </c>
       <c r="AH4">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AJ4">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
@@ -1148,25 +1148,25 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>L0.png</t>
         </is>
       </c>
       <c r="AW4">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1182,112 +1182,112 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>-111</v>
+        <v>-44</v>
       </c>
       <c r="B5">
-        <v>-269</v>
+        <v>-379</v>
       </c>
       <c r="C5">
-        <v>-331</v>
+        <v>-284</v>
       </c>
       <c r="D5">
-        <v>-40</v>
+        <v>-131</v>
       </c>
       <c r="E5">
-        <v>-118</v>
+        <v>-213</v>
       </c>
       <c r="F5">
-        <v>-263</v>
+        <v>-43</v>
       </c>
       <c r="G5">
-        <v>188</v>
+        <v>288</v>
       </c>
       <c r="H5">
-        <v>345</v>
+        <v>211</v>
       </c>
       <c r="I5">
-        <v>268</v>
+        <v>117</v>
       </c>
       <c r="J5">
-        <v>341</v>
+        <v>38</v>
       </c>
       <c r="K5">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="L5">
-        <v>112</v>
+        <v>212</v>
       </c>
       <c r="M5">
-        <v>-111</v>
+        <v>-131</v>
       </c>
       <c r="N5">
-        <v>-264</v>
+        <v>-381</v>
       </c>
       <c r="O5">
-        <v>-31</v>
+        <v>-292</v>
       </c>
       <c r="P5">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="Q5">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="R5">
-        <v>336</v>
+        <v>41</v>
       </c>
       <c r="S5">
-        <v>-195</v>
+        <v>-133</v>
       </c>
       <c r="T5">
-        <v>-335</v>
+        <v>-214</v>
       </c>
       <c r="U5">
-        <v>-37</v>
+        <v>-375</v>
       </c>
       <c r="V5">
-        <v>264</v>
+        <v>214</v>
       </c>
       <c r="W5">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="X5">
-        <v>182</v>
+        <v>370</v>
       </c>
       <c r="Y5">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="Z5">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AB5">
         <v>270</v>
       </c>
       <c r="AC5">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AD5">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AE5">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AH5">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
@@ -1306,19 +1306,19 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AQ5" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -1350,11 +1350,11 @@
         </is>
       </c>
       <c r="AW5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>left</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1370,143 +1370,143 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>-267</v>
+        <v>-381</v>
       </c>
       <c r="B6">
-        <v>-108</v>
+        <v>-202</v>
       </c>
       <c r="C6">
-        <v>-32</v>
+        <v>-129</v>
       </c>
       <c r="D6">
-        <v>-40</v>
+        <v>-125</v>
       </c>
       <c r="E6">
-        <v>-181</v>
+        <v>-372</v>
       </c>
       <c r="F6">
-        <v>-113</v>
+        <v>-293</v>
       </c>
       <c r="G6">
-        <v>35</v>
+        <v>374</v>
       </c>
       <c r="H6">
-        <v>262</v>
+        <v>41</v>
       </c>
       <c r="I6">
+        <v>121</v>
+      </c>
+      <c r="J6">
+        <v>288</v>
+      </c>
+      <c r="K6">
+        <v>209</v>
+      </c>
+      <c r="L6">
         <v>117</v>
       </c>
-      <c r="J6">
-        <v>189</v>
-      </c>
-      <c r="K6">
-        <v>339</v>
-      </c>
-      <c r="L6">
-        <v>267</v>
-      </c>
       <c r="M6">
-        <v>-260</v>
+        <v>-374</v>
       </c>
       <c r="N6">
-        <v>-184</v>
+        <v>-125</v>
       </c>
       <c r="O6">
-        <v>-108</v>
+        <v>-294</v>
       </c>
       <c r="P6">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="Q6">
-        <v>338</v>
+        <v>200</v>
       </c>
       <c r="R6">
-        <v>180</v>
+        <v>371</v>
       </c>
       <c r="S6">
-        <v>-32</v>
+        <v>-286</v>
       </c>
       <c r="T6">
-        <v>-116</v>
+        <v>-43</v>
       </c>
       <c r="U6">
-        <v>-194</v>
+        <v>-126</v>
       </c>
       <c r="V6">
-        <v>187</v>
+        <v>373</v>
       </c>
       <c r="W6">
-        <v>109</v>
+        <v>36</v>
       </c>
       <c r="X6">
-        <v>331</v>
+        <v>123</v>
       </c>
       <c r="Y6">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="Z6">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AB6">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AD6">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AE6">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AH6">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AJ6">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AQ6" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="AW6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
@@ -1558,153 +1558,153 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>-36</v>
+        <v>-207</v>
       </c>
       <c r="B7">
-        <v>-268</v>
+        <v>-296</v>
       </c>
       <c r="C7">
-        <v>-183</v>
+        <v>-41</v>
       </c>
       <c r="D7">
-        <v>-42</v>
+        <v>-299</v>
       </c>
       <c r="E7">
-        <v>-264</v>
+        <v>-43</v>
       </c>
       <c r="F7">
-        <v>-180</v>
+        <v>-126</v>
       </c>
       <c r="G7">
-        <v>106</v>
+        <v>40</v>
       </c>
       <c r="H7">
-        <v>43</v>
+        <v>132</v>
       </c>
       <c r="I7">
-        <v>337</v>
+        <v>299</v>
       </c>
       <c r="J7">
-        <v>334</v>
+        <v>36</v>
       </c>
       <c r="K7">
-        <v>37</v>
+        <v>288</v>
       </c>
       <c r="L7">
-        <v>106</v>
+        <v>211</v>
       </c>
       <c r="M7">
-        <v>-33</v>
+        <v>-214</v>
       </c>
       <c r="N7">
-        <v>-110</v>
+        <v>-286</v>
       </c>
       <c r="O7">
-        <v>-257</v>
+        <v>-41</v>
       </c>
       <c r="P7">
-        <v>336</v>
+        <v>290</v>
       </c>
       <c r="Q7">
-        <v>268</v>
+        <v>374</v>
       </c>
       <c r="R7">
-        <v>38</v>
+        <v>131</v>
       </c>
       <c r="S7">
-        <v>-261</v>
+        <v>-37</v>
       </c>
       <c r="T7">
-        <v>-115</v>
+        <v>-295</v>
       </c>
       <c r="U7">
-        <v>-187</v>
+        <v>-216</v>
       </c>
       <c r="V7">
-        <v>257</v>
+        <v>44</v>
       </c>
       <c r="W7">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="X7">
-        <v>44</v>
+        <v>370</v>
       </c>
       <c r="Y7">
         <v>90</v>
       </c>
       <c r="Z7">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AB7">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AC7">
         <v>270</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AE7">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AF7">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AG7">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AH7">
         <v>180</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AJ7">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="AW7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
@@ -1746,85 +1746,85 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>-185</v>
+        <v>-287</v>
       </c>
       <c r="B8">
-        <v>-43</v>
+        <v>-203</v>
       </c>
       <c r="C8">
-        <v>-334</v>
+        <v>-127</v>
       </c>
       <c r="D8">
-        <v>-39</v>
+        <v>-123</v>
       </c>
       <c r="E8">
-        <v>-266</v>
+        <v>-205</v>
       </c>
       <c r="F8">
-        <v>-181</v>
+        <v>-283</v>
       </c>
       <c r="G8">
-        <v>181</v>
+        <v>296</v>
       </c>
       <c r="H8">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="I8">
-        <v>262</v>
+        <v>42</v>
       </c>
       <c r="J8">
-        <v>340</v>
+        <v>124</v>
       </c>
       <c r="K8">
+        <v>373</v>
+      </c>
+      <c r="L8">
+        <v>296</v>
+      </c>
+      <c r="M8">
+        <v>-288</v>
+      </c>
+      <c r="N8">
+        <v>-129</v>
+      </c>
+      <c r="O8">
+        <v>-206</v>
+      </c>
+      <c r="P8">
+        <v>283</v>
+      </c>
+      <c r="Q8">
+        <v>200</v>
+      </c>
+      <c r="R8">
+        <v>366</v>
+      </c>
+      <c r="S8">
+        <v>-49</v>
+      </c>
+      <c r="T8">
+        <v>-200</v>
+      </c>
+      <c r="U8">
+        <v>-288</v>
+      </c>
+      <c r="V8">
+        <v>376</v>
+      </c>
+      <c r="W8">
+        <v>287</v>
+      </c>
+      <c r="X8">
         <v>44</v>
       </c>
-      <c r="L8">
-        <v>260</v>
-      </c>
-      <c r="M8">
-        <v>-185</v>
-      </c>
-      <c r="N8">
-        <v>-41</v>
-      </c>
-      <c r="O8">
-        <v>-115</v>
-      </c>
-      <c r="P8">
-        <v>31</v>
-      </c>
-      <c r="Q8">
-        <v>334</v>
-      </c>
-      <c r="R8">
-        <v>116</v>
-      </c>
-      <c r="S8">
-        <v>-117</v>
-      </c>
-      <c r="T8">
-        <v>-43</v>
-      </c>
-      <c r="U8">
-        <v>-334</v>
-      </c>
-      <c r="V8">
-        <v>44</v>
-      </c>
-      <c r="W8">
-        <v>255</v>
-      </c>
-      <c r="X8">
-        <v>106</v>
-      </c>
       <c r="Y8">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="Z8">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AB8">
         <v>180</v>
@@ -1833,16 +1833,16 @@
         <v>270</v>
       </c>
       <c r="AD8">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AE8">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AF8">
         <v>90</v>
       </c>
       <c r="AG8">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AH8">
         <v>0</v>
@@ -1934,85 +1934,85 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>-118</v>
+        <v>-282</v>
       </c>
       <c r="B9">
-        <v>-265</v>
+        <v>-132</v>
       </c>
       <c r="C9">
-        <v>-334</v>
+        <v>-44</v>
       </c>
       <c r="D9">
-        <v>-262</v>
+        <v>-203</v>
       </c>
       <c r="E9">
-        <v>-340</v>
+        <v>-130</v>
       </c>
       <c r="F9">
-        <v>-184</v>
+        <v>-40</v>
       </c>
       <c r="G9">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H9">
-        <v>181</v>
+        <v>123</v>
       </c>
       <c r="I9">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="J9">
-        <v>263</v>
+        <v>202</v>
       </c>
       <c r="K9">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="L9">
-        <v>184</v>
+        <v>288</v>
       </c>
       <c r="M9">
-        <v>-42</v>
+        <v>-132</v>
       </c>
       <c r="N9">
-        <v>-258</v>
+        <v>-200</v>
       </c>
       <c r="O9">
-        <v>-184</v>
+        <v>-40</v>
       </c>
       <c r="P9">
-        <v>34</v>
+        <v>296</v>
       </c>
       <c r="Q9">
-        <v>110</v>
+        <v>203</v>
       </c>
       <c r="R9">
-        <v>267</v>
+        <v>128</v>
       </c>
       <c r="S9">
-        <v>-180</v>
+        <v>-367</v>
       </c>
       <c r="T9">
-        <v>-116</v>
+        <v>-117</v>
       </c>
       <c r="U9">
-        <v>-332</v>
+        <v>-212</v>
       </c>
       <c r="V9">
-        <v>117</v>
+        <v>210</v>
       </c>
       <c r="W9">
-        <v>262</v>
+        <v>128</v>
       </c>
       <c r="X9">
-        <v>331</v>
+        <v>290</v>
       </c>
       <c r="Y9">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="Z9">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AA9">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AB9">
         <v>270</v>
@@ -2024,22 +2024,22 @@
         <v>0</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AF9">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AH9">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AJ9">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
@@ -2058,14 +2058,14 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AP9" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="AW9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
@@ -2122,76 +2122,76 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>-106</v>
+        <v>-39</v>
       </c>
       <c r="B10">
-        <v>-344</v>
+        <v>-117</v>
       </c>
       <c r="C10">
-        <v>-189</v>
+        <v>-368</v>
       </c>
       <c r="D10">
-        <v>-109</v>
+        <v>-42</v>
       </c>
       <c r="E10">
-        <v>-330</v>
+        <v>-127</v>
       </c>
       <c r="F10">
-        <v>-257</v>
+        <v>-201</v>
       </c>
       <c r="G10">
+        <v>208</v>
+      </c>
+      <c r="H10">
+        <v>380</v>
+      </c>
+      <c r="I10">
+        <v>123</v>
+      </c>
+      <c r="J10">
         <v>35</v>
       </c>
-      <c r="H10">
-        <v>117</v>
-      </c>
-      <c r="I10">
-        <v>257</v>
-      </c>
-      <c r="J10">
-        <v>268</v>
-      </c>
       <c r="K10">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="L10">
-        <v>183</v>
+        <v>380</v>
       </c>
       <c r="M10">
-        <v>-30</v>
+        <v>-295</v>
       </c>
       <c r="N10">
-        <v>-186</v>
+        <v>-207</v>
       </c>
       <c r="O10">
-        <v>-266</v>
+        <v>-122</v>
       </c>
       <c r="P10">
-        <v>259</v>
+        <v>42</v>
       </c>
       <c r="Q10">
-        <v>41</v>
+        <v>127</v>
       </c>
       <c r="R10">
-        <v>106</v>
+        <v>372</v>
       </c>
       <c r="S10">
-        <v>-194</v>
+        <v>-368</v>
       </c>
       <c r="T10">
-        <v>-44</v>
+        <v>-288</v>
       </c>
       <c r="U10">
-        <v>-117</v>
+        <v>-118</v>
       </c>
       <c r="V10">
-        <v>31</v>
+        <v>288</v>
       </c>
       <c r="W10">
-        <v>111</v>
+        <v>367</v>
       </c>
       <c r="X10">
-        <v>256</v>
+        <v>42</v>
       </c>
       <c r="Y10">
         <v>270</v>
@@ -2200,38 +2200,38 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AB10">
         <v>90</v>
       </c>
       <c r="AC10">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AD10">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AF10">
         <v>180</v>
       </c>
       <c r="AG10">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AI10">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2290,7 +2290,7 @@
         </is>
       </c>
       <c r="AW10">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
@@ -2310,97 +2310,97 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>-191</v>
+        <v>-37</v>
       </c>
       <c r="B11">
-        <v>-108</v>
+        <v>-121</v>
       </c>
       <c r="C11">
-        <v>-344</v>
+        <v>-285</v>
       </c>
       <c r="D11">
-        <v>-265</v>
+        <v>-214</v>
       </c>
       <c r="E11">
-        <v>-118</v>
+        <v>-376</v>
       </c>
       <c r="F11">
-        <v>-44</v>
+        <v>-120</v>
       </c>
       <c r="G11">
+        <v>43</v>
+      </c>
+      <c r="H11">
+        <v>204</v>
+      </c>
+      <c r="I11">
+        <v>298</v>
+      </c>
+      <c r="J11">
         <v>118</v>
       </c>
-      <c r="H11">
-        <v>39</v>
-      </c>
-      <c r="I11">
-        <v>340</v>
-      </c>
-      <c r="J11">
-        <v>267</v>
-      </c>
       <c r="K11">
-        <v>343</v>
+        <v>296</v>
       </c>
       <c r="L11">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="M11">
-        <v>-344</v>
+        <v>-205</v>
       </c>
       <c r="N11">
-        <v>-37</v>
+        <v>-125</v>
       </c>
       <c r="O11">
-        <v>-269</v>
+        <v>-286</v>
       </c>
       <c r="P11">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="Q11">
-        <v>188</v>
+        <v>380</v>
       </c>
       <c r="R11">
-        <v>107</v>
+        <v>202</v>
       </c>
       <c r="S11">
-        <v>-112</v>
+        <v>-124</v>
       </c>
       <c r="T11">
-        <v>-267</v>
+        <v>-366</v>
       </c>
       <c r="U11">
-        <v>-187</v>
+        <v>-45</v>
       </c>
       <c r="V11">
-        <v>266</v>
+        <v>298</v>
       </c>
       <c r="W11">
-        <v>187</v>
+        <v>41</v>
       </c>
       <c r="X11">
-        <v>39</v>
+        <v>369</v>
       </c>
       <c r="Y11">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="Z11">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AA11">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AC11">
         <v>0</v>
       </c>
       <c r="AD11">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AE11">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AF11">
         <v>270</v>
@@ -2409,13 +2409,13 @@
         <v>0</v>
       </c>
       <c r="AH11">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AI11">
         <v>90</v>
       </c>
       <c r="AJ11">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
@@ -2444,19 +2444,19 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>L0.png</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
           <t>T0.png</t>
         </is>
       </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>L0.png</t>
-        </is>
-      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>L0.png</t>
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="AW11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
@@ -2498,109 +2498,109 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>-267</v>
+        <v>-203</v>
       </c>
       <c r="B12">
-        <v>-115</v>
+        <v>-289</v>
       </c>
       <c r="C12">
-        <v>-339</v>
+        <v>-129</v>
       </c>
       <c r="D12">
-        <v>-333</v>
+        <v>-379</v>
       </c>
       <c r="E12">
-        <v>-189</v>
+        <v>-37</v>
       </c>
       <c r="F12">
-        <v>-108</v>
+        <v>-130</v>
       </c>
       <c r="G12">
-        <v>257</v>
+        <v>367</v>
       </c>
       <c r="H12">
-        <v>114</v>
+        <v>202</v>
       </c>
       <c r="I12">
-        <v>192</v>
+        <v>294</v>
       </c>
       <c r="J12">
-        <v>342</v>
+        <v>203</v>
       </c>
       <c r="K12">
-        <v>39</v>
+        <v>296</v>
       </c>
       <c r="L12">
-        <v>256</v>
+        <v>123</v>
       </c>
       <c r="M12">
-        <v>-266</v>
+        <v>-379</v>
       </c>
       <c r="N12">
-        <v>-343</v>
+        <v>-207</v>
       </c>
       <c r="O12">
-        <v>-110</v>
+        <v>-47</v>
       </c>
       <c r="P12">
-        <v>259</v>
+        <v>43</v>
       </c>
       <c r="Q12">
-        <v>108</v>
+        <v>368</v>
       </c>
       <c r="R12">
-        <v>183</v>
+        <v>290</v>
       </c>
       <c r="S12">
-        <v>-39</v>
+        <v>-42</v>
       </c>
       <c r="T12">
-        <v>-262</v>
+        <v>-294</v>
       </c>
       <c r="U12">
-        <v>-119</v>
+        <v>-381</v>
       </c>
       <c r="V12">
-        <v>333</v>
+        <v>284</v>
       </c>
       <c r="W12">
-        <v>266</v>
+        <v>200</v>
       </c>
       <c r="X12">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="Y12">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AA12">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AB12">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="AC12">
         <v>270</v>
       </c>
       <c r="AD12">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AF12">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AH12">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AJ12">
         <v>180</v>
@@ -2647,12 +2647,12 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -2666,11 +2666,11 @@
         </is>
       </c>
       <c r="AW12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>right</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2686,109 +2686,109 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>-31</v>
+        <v>-44</v>
       </c>
       <c r="B13">
-        <v>-342</v>
+        <v>-296</v>
       </c>
       <c r="C13">
-        <v>-117</v>
+        <v>-212</v>
       </c>
       <c r="D13">
-        <v>-260</v>
+        <v>-212</v>
       </c>
       <c r="E13">
-        <v>-187</v>
+        <v>-46</v>
       </c>
       <c r="F13">
-        <v>-36</v>
+        <v>-119</v>
       </c>
       <c r="G13">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="H13">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="I13">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="J13">
-        <v>259</v>
+        <v>44</v>
       </c>
       <c r="K13">
-        <v>120</v>
+        <v>299</v>
       </c>
       <c r="L13">
-        <v>41</v>
+        <v>203</v>
       </c>
       <c r="M13">
-        <v>-110</v>
+        <v>-368</v>
       </c>
       <c r="N13">
-        <v>-32</v>
+        <v>-47</v>
       </c>
       <c r="O13">
-        <v>-256</v>
+        <v>-202</v>
       </c>
       <c r="P13">
-        <v>44</v>
+        <v>202</v>
       </c>
       <c r="Q13">
-        <v>110</v>
+        <v>366</v>
       </c>
       <c r="R13">
-        <v>261</v>
+        <v>122</v>
       </c>
       <c r="S13">
-        <v>-343</v>
+        <v>-118</v>
       </c>
       <c r="T13">
-        <v>-116</v>
+        <v>-297</v>
       </c>
       <c r="U13">
-        <v>-258</v>
+        <v>-42</v>
       </c>
       <c r="V13">
-        <v>187</v>
+        <v>37</v>
       </c>
       <c r="W13">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="X13">
-        <v>117</v>
+        <v>211</v>
       </c>
       <c r="Y13">
         <v>90</v>
       </c>
       <c r="Z13">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AA13">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AB13">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AD13">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="AG13">
-        <v>90</v>
+        <v>270</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AI13">
-        <v>270</v>
+        <v>90</v>
       </c>
       <c r="AJ13">
         <v>180</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>L0.png</t>
+          <t>T0.png</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>T0.png</t>
+          <t>L0.png</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
@@ -2854,7 +2854,7 @@
         </is>
       </c>
       <c r="AW13">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
